--- a/catalog-files/Islamabad_Tea_Professional.xlsx
+++ b/catalog-files/Islamabad_Tea_Professional.xlsx
@@ -1865,7 +1865,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Leaf Blend offers a leaf tea blend made with tea sourced from Kenya.
 Pack size: 425 g.
-Packaging: Jar.</t>
+Packaging: Jar.
+Serving options: hot or iced tea.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1960,7 +1961,8 @@
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
-Pack size: 25 g.</t>
+Pack size: 25 g.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2056,7 +2058,8 @@
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Gold is a tea blend made with Kenyan BP1 tea granules.
 Pack size: 25 g.
-Packaging: Hard pack.</t>
+Packaging: Hard pack.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2248,7 +2251,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
 Pack size: 350 g.
-Packaging: Pouch.</t>
+Packaging: Pouch.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2343,7 +2347,8 @@
       <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Blend is a tea blend made with Kenyan BP1 tea granules.
-Pack size: 170 g.</t>
+Pack size: 170 g.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2439,7 +2444,10 @@
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Gold is a tea blend made with Kenyan BP1 tea granules.
 Pack size: 170 g.
-Packaging: Hard pack.</t>
+Packaging: Hard pack.
+Tea type: Kenyan BP1 tea granules (dana).
+A black tea blend with a strong character, rich colour and full-bodied flavour, suited to everyday tea and traditional Pakistani chai.
+Storage: Store in a cool, dry place away from direct sunlight and moisture. Keep the pack tightly closed after opening.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2534,7 +2542,8 @@
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Blend is a tea blend made with Kenyan BP1 tea granules.
-Pack size: 430 g.</t>
+Pack size: 430 g.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2630,7 +2639,8 @@
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Blend is a tea blend made with Kenyan BP1 tea granules.
 Pack size: 85 g.
-Packaging: Hard pack.</t>
+Packaging: Hard pack.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2726,7 +2736,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
 Pack size: 85 g.
-Packaging: Hard pack.</t>
+Packaging: Hard pack.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2822,7 +2833,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
 Pack size: 900 g.
-Packaging: Pouch.</t>
+Packaging: Pouch.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2917,7 +2929,8 @@
       <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Blend is a tea blend made with Kenyan BP1 tea granules.
-Pack size: 900 g.</t>
+Pack size: 900 g.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3013,7 +3026,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
 Pack size: 430 g.
-Packaging: Pouch.</t>
+Packaging: Pouch.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3874,7 +3888,8 @@
       <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Islamabad Dawoodi Blend is a tea blend made with Kenyan BP1 tea granules.
-Pack size: 1600 g.</t>
+Pack size: 1600 g.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4352,7 +4367,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
 Pack size: 170 g.
-Packaging: Hard pack.</t>
+Packaging: Hard pack.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4447,7 +4463,9 @@
       <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">Islamabad Tea Leaf Blend offers a leaf tea blend made with tea sourced from Kenya.
-Packaging: Pouch.</t>
+Packaging: Pouch.
+Pack-size note: The product title states 1600 g; the source description states 1650 g. Confirm the pack size before ordering.
+Serving options: hot or iced tea.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4543,7 +4561,8 @@
         <is>
           <t xml:space="preserve">Islamabad Tea Super Dana is a blend of Kenyan BP1 tea granules.
 Pack size: 170 g.
-Packaging: Pouch.</t>
+Packaging: Pouch.
+Tea type: Kenyan BP1 tea granules (dana).</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
